--- a/results/consolidated/Distributional_Metrics.xlsx
+++ b/results/consolidated/Distributional_Metrics.xlsx
@@ -444,10 +444,10 @@
         <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0801949490474081</v>
+        <v>0.0821149017870329</v>
       </c>
       <c r="D2" t="n">
-        <v>0.157636568166926</v>
+        <v>0.156206358339881</v>
       </c>
       <c r="E2" t="n">
         <v>3.16745387149051</v>
@@ -470,7 +470,7 @@
         <v>0.065869147836361</v>
       </c>
       <c r="D3" t="n">
-        <v>0.136087191731774</v>
+        <v>0.136462363003612</v>
       </c>
       <c r="E3" t="n">
         <v>3.1500756077916</v>
@@ -490,10 +490,10 @@
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0550878747600059</v>
+        <v>0.0503618372470831</v>
       </c>
       <c r="D4" t="n">
-        <v>0.119678882643744</v>
+        <v>0.109570277748539</v>
       </c>
       <c r="E4" t="n">
         <v>3.24083533075908</v>
@@ -513,10 +513,10 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0769457982572737</v>
+        <v>0.0803426377196869</v>
       </c>
       <c r="D5" t="n">
-        <v>0.174195601774061</v>
+        <v>0.174467468214253</v>
       </c>
       <c r="E5" t="n">
         <v>2.73031669669996</v>
@@ -536,19 +536,19 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0686752326096588</v>
+        <v>0.0663122138531975</v>
       </c>
       <c r="D6" t="n">
-        <v>0.164512008143137</v>
+        <v>0.159749891039588</v>
       </c>
       <c r="E6" t="n">
-        <v>2.95319480751647</v>
+        <v>2.95319480751651</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.290767344618739</v>
+        <v>-0.290767344618738</v>
       </c>
       <c r="G6" t="n">
-        <v>17.5934929069273</v>
+        <v>17.5934929069274</v>
       </c>
     </row>
     <row r="7">
@@ -559,10 +559,10 @@
         <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0824102791315906</v>
+        <v>0.0939299955693398</v>
       </c>
       <c r="D7" t="n">
-        <v>0.209776640279721</v>
+        <v>0.219618266406986</v>
       </c>
       <c r="E7" t="n">
         <v>2.60571749545656</v>
@@ -582,10 +582,10 @@
         <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>0.304829419583518</v>
+        <v>0.310146211785556</v>
       </c>
       <c r="D8" t="n">
-        <v>0.608208859026904</v>
+        <v>0.602427639066635</v>
       </c>
       <c r="E8" t="n">
         <v>1.23795205887821</v>
@@ -605,10 +605,10 @@
         <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>0.344040762073549</v>
+        <v>0.334514842711564</v>
       </c>
       <c r="D9" t="n">
-        <v>0.668035615819896</v>
+        <v>0.666307752543019</v>
       </c>
       <c r="E9" t="n">
         <v>1.07904672660092</v>
@@ -627,21 +627,11 @@
       <c r="B10" t="s">
         <v>10</v>
       </c>
-      <c r="C10" t="n">
-        <v>0.0298331118003249</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.0581859466874666</v>
-      </c>
-      <c r="E10" t="n">
-        <v>3.72044075198291</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.470402467111507</v>
-      </c>
-      <c r="G10" t="n">
-        <v>4.17017071750532</v>
-      </c>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
@@ -651,19 +641,19 @@
         <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0540540540540541</v>
+        <v>0.163491360212672</v>
       </c>
       <c r="D11" t="n">
-        <v>0.14113158447845</v>
+        <v>0.236785111906135</v>
       </c>
       <c r="E11" t="n">
-        <v>2.89990750691682</v>
+        <v>3.91037315514876</v>
       </c>
       <c r="F11" t="n">
-        <v>0.548908556313725</v>
+        <v>-1.87959438539939</v>
       </c>
       <c r="G11" t="n">
-        <v>17.3002692609863</v>
+        <v>13.1827363509551</v>
       </c>
     </row>
     <row r="12">
@@ -673,21 +663,11 @@
       <c r="B12" t="s">
         <v>12</v>
       </c>
-      <c r="C12" t="n">
-        <v>0.0642445724412938</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.149860776530063</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2.88268362373451</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.118318091282215</v>
-      </c>
-      <c r="G12" t="n">
-        <v>12.9374659452236</v>
-      </c>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
@@ -696,21 +676,11 @@
       <c r="B13" t="s">
         <v>13</v>
       </c>
-      <c r="C13" t="n">
-        <v>0.0599616009452075</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.167481256957086</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2.60404643848225</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1.17076818961658</v>
-      </c>
-      <c r="G13" t="n">
-        <v>21.606779230327</v>
-      </c>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
@@ -720,10 +690,10 @@
         <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0998375424604933</v>
+        <v>0.0958499483089647</v>
       </c>
       <c r="D14" t="n">
-        <v>0.210827810171211</v>
+        <v>0.208802205050974</v>
       </c>
       <c r="E14" t="n">
         <v>2.80686466616841</v>
@@ -743,10 +713,10 @@
         <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0954068822921282</v>
+        <v>0.0899424014178112</v>
       </c>
       <c r="D15" t="n">
-        <v>0.208098918338524</v>
+        <v>0.207561420642828</v>
       </c>
       <c r="E15" t="n">
         <v>2.45210132213632</v>
@@ -766,10 +736,10 @@
         <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0700044306601684</v>
+        <v>0.0704474966770049</v>
       </c>
       <c r="D16" t="n">
-        <v>0.167467331084733</v>
+        <v>0.163173855721279</v>
       </c>
       <c r="E16" t="n">
         <v>2.80984099881588</v>
@@ -789,19 +759,19 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0998375424604933</v>
+        <v>0.102052872544676</v>
       </c>
       <c r="D17" t="n">
-        <v>0.225404071214227</v>
+        <v>0.225304617973403</v>
       </c>
       <c r="E17" t="n">
         <v>2.50881375230642</v>
       </c>
       <c r="F17" t="n">
-        <v>1.74401935510357</v>
+        <v>1.74401935510359</v>
       </c>
       <c r="G17" t="n">
-        <v>33.9540592100708</v>
+        <v>33.9540592100711</v>
       </c>
     </row>
     <row r="18">
@@ -812,10 +782,10 @@
         <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0954068822921282</v>
+        <v>0.0911239107960419</v>
       </c>
       <c r="D18" t="n">
-        <v>0.216318983199867</v>
+        <v>0.215774827694079</v>
       </c>
       <c r="E18" t="n">
         <v>2.64500822858612</v>
@@ -835,10 +805,10 @@
         <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>0.111948013587358</v>
+        <v>0.111800324915079</v>
       </c>
       <c r="D19" t="n">
-        <v>0.266266426416811</v>
+        <v>0.260317717474662</v>
       </c>
       <c r="E19" t="n">
         <v>2.31734724008197</v>
@@ -858,10 +828,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0497710825579678</v>
+        <v>0.0451927337173239</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0936113993413482</v>
+        <v>0.0938271338711843</v>
       </c>
       <c r="E20" t="n">
         <v>3.30362050153608</v>
@@ -881,10 +851,10 @@
         <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0364791020528725</v>
+        <v>0.0443066016836509</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0792599135831264</v>
+        <v>0.0860304627306064</v>
       </c>
       <c r="E21" t="n">
         <v>3.55462703307353</v>
@@ -904,10 +874,10 @@
         <v>10</v>
       </c>
       <c r="C22" t="n">
-        <v>0.176044897356373</v>
+        <v>0.173091123910796</v>
       </c>
       <c r="D22" t="n">
-        <v>0.24600444516633</v>
+        <v>0.248869546555533</v>
       </c>
       <c r="E22" t="n">
         <v>3.38654768167346</v>
@@ -927,19 +897,19 @@
         <v>11</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0527248560035445</v>
+        <v>0.0573032048441885</v>
       </c>
       <c r="D23" t="n">
-        <v>0.14141188223432</v>
+        <v>0.144488812362079</v>
       </c>
       <c r="E23" t="n">
-        <v>2.84506444426865</v>
+        <v>2.84506444423159</v>
       </c>
       <c r="F23" t="n">
-        <v>0.736277432094375</v>
+        <v>0.736277432110608</v>
       </c>
       <c r="G23" t="n">
-        <v>17.7952620064131</v>
+        <v>17.7952620065376</v>
       </c>
     </row>
     <row r="24">
@@ -950,19 +920,19 @@
         <v>12</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0573032048441885</v>
+        <v>0.0575985821887461</v>
       </c>
       <c r="D24" t="n">
-        <v>0.141145606787678</v>
+        <v>0.13815579128666</v>
       </c>
       <c r="E24" t="n">
-        <v>2.96328437147108</v>
+        <v>2.96328437151777</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.334887482435224</v>
+        <v>-0.334887482419656</v>
       </c>
       <c r="G24" t="n">
-        <v>13.4862683618879</v>
+        <v>13.4862683618155</v>
       </c>
     </row>
     <row r="25">
@@ -973,10 +943,10 @@
         <v>13</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0691182986264954</v>
+        <v>0.0666075911977551</v>
       </c>
       <c r="D25" t="n">
-        <v>0.179050301542886</v>
+        <v>0.180971508720854</v>
       </c>
       <c r="E25" t="n">
         <v>2.58537455920498</v>
@@ -1030,22 +1000,22 @@
         <v>15</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0954068822921282</v>
+        <v>0.0935361591099296</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0976222123763107</v>
+        <v>0.0934869295525033</v>
       </c>
       <c r="D2" t="n">
-        <v>0.215730590070896</v>
+        <v>0.213489107426204</v>
       </c>
       <c r="E2" t="n">
-        <v>0.213573396685539</v>
+        <v>0.212288516372527</v>
       </c>
       <c r="F2" t="n">
         <v>2.58999603468252</v>
       </c>
       <c r="G2" t="n">
-        <v>0.424905513461851</v>
+        <v>0.424905513461854</v>
       </c>
       <c r="H2" t="n">
         <v>27.86455188624</v>
@@ -1056,25 +1026,25 @@
         <v>14</v>
       </c>
       <c r="B3" t="n">
-        <v>0.142827253482991</v>
+        <v>0.269384138236597</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0621030866932506</v>
+        <v>0.310146211785556</v>
       </c>
       <c r="D3" t="n">
-        <v>0.298817339916644</v>
+        <v>0.501840167838596</v>
       </c>
       <c r="E3" t="n">
-        <v>0.158671016743574</v>
+        <v>0.602427639066635</v>
       </c>
       <c r="F3" t="n">
-        <v>2.40401285109927</v>
+        <v>2.07579064687596</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0111743714512416</v>
+        <v>-1.41834597281029</v>
       </c>
       <c r="H3" t="n">
-        <v>79.0060012353707</v>
+        <v>143.734686203046</v>
       </c>
     </row>
     <row r="4">
@@ -1082,25 +1052,25 @@
         <v>16</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0735735735735736</v>
+        <v>0.0740166395904101</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0550140304238665</v>
+        <v>0.0574508935164673</v>
       </c>
       <c r="D4" t="n">
-        <v>0.146747258109281</v>
+        <v>0.148723875921153</v>
       </c>
       <c r="E4" t="n">
-        <v>0.141278744510999</v>
+        <v>0.14132230182437</v>
       </c>
       <c r="F4" t="n">
-        <v>3.10641976520463</v>
+        <v>3.10641976520623</v>
       </c>
       <c r="G4" t="n">
-        <v>0.199479356316453</v>
+        <v>0.199479356321753</v>
       </c>
       <c r="H4" t="n">
-        <v>13.0226291819186</v>
+        <v>13.0226291819273</v>
       </c>
     </row>
     <row r="5">
@@ -1108,16 +1078,16 @@
         <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>0.071530546940383</v>
+        <v>0.0731551223354502</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0728105154334663</v>
+        <v>0.0733274257864422</v>
       </c>
       <c r="D5" t="n">
-        <v>0.160314482123227</v>
+        <v>0.159345770792143</v>
       </c>
       <c r="E5" t="n">
-        <v>0.161074288155032</v>
+        <v>0.157978124689735</v>
       </c>
       <c r="F5" t="n">
         <v>2.9745989682857</v>

--- a/results/consolidated/Distributional_Metrics.xlsx
+++ b/results/consolidated/Distributional_Metrics.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t xml:space="preserve">Model</t>
   </si>
@@ -27,13 +27,22 @@
     <t xml:space="preserve">Wasserstein_distance</t>
   </si>
   <si>
-    <t xml:space="preserve">Tail_index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skewness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurtosis</t>
+    <t xml:space="preserve">Tail_index_Std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skewness_Std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurtosis_Std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tail_index_NF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skewness_NF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurtosis_NF</t>
   </si>
   <si>
     <t xml:space="preserve">sGARCH</t>
@@ -78,13 +87,22 @@
     <t xml:space="preserve">median_Wasserstein</t>
   </si>
   <si>
-    <t xml:space="preserve">mean_Tail_index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_Skewness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_Kurtosis</t>
+    <t xml:space="preserve">mean_Tail_index_Std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_Skewness_Std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_Kurtosis_Std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_Tail_index_NF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_Skewness_NF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_Kurtosis_NF</t>
   </si>
 </sst>
 </file>
@@ -435,22 +453,31 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0821149017870329</v>
+        <v>0.076650420912716</v>
       </c>
       <c r="D2" t="n">
-        <v>0.156206358339881</v>
+        <v>0.160389152361435</v>
       </c>
       <c r="E2" t="n">
-        <v>3.16745387149051</v>
+        <v>3.15631031146281</v>
       </c>
       <c r="F2" t="n">
         <v>-0.418138070850439</v>
@@ -458,45 +485,63 @@
       <c r="G2" t="n">
         <v>8.97776447874992</v>
       </c>
+      <c r="H2" t="n">
+        <v>4.63308831976915</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-0.0138493356016358</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.96197909302964</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>0.065869147836361</v>
+        <v>0.0654260818195244</v>
       </c>
       <c r="D3" t="n">
-        <v>0.136462363003612</v>
+        <v>0.147674105852211</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1500756077916</v>
+        <v>3.15524434405118</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.128815522969519</v>
+        <v>-0.12881552296952</v>
       </c>
       <c r="G3" t="n">
         <v>7.18162205654484</v>
       </c>
+      <c r="H3" t="n">
+        <v>4.61893274833412</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.000438873877783509</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.84982224717142</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0503618372470831</v>
+        <v>0.0555309407768424</v>
       </c>
       <c r="D4" t="n">
-        <v>0.109570277748539</v>
+        <v>0.116236848525405</v>
       </c>
       <c r="E4" t="n">
-        <v>3.24083533075908</v>
+        <v>3.25856947811445</v>
       </c>
       <c r="F4" t="n">
         <v>0.515500113795784</v>
@@ -504,22 +549,31 @@
       <c r="G4" t="n">
         <v>6.36143305583346</v>
       </c>
+      <c r="H4" t="n">
+        <v>4.74373578764116</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.0370981127070806</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.97589345631208</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0803426377196869</v>
+        <v>0.0711859400383991</v>
       </c>
       <c r="D5" t="n">
-        <v>0.174467468214253</v>
+        <v>0.171341473829878</v>
       </c>
       <c r="E5" t="n">
-        <v>2.73031669669996</v>
+        <v>2.72229452863646</v>
       </c>
       <c r="F5" t="n">
         <v>0.691826796604542</v>
@@ -527,22 +581,31 @@
       <c r="G5" t="n">
         <v>13.5774726700034</v>
       </c>
+      <c r="H5" t="n">
+        <v>4.70467977372323</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0266518432484328</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.0086323404525</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0663122138531975</v>
+        <v>0.0674937232314281</v>
       </c>
       <c r="D6" t="n">
-        <v>0.159749891039588</v>
+        <v>0.166974796151183</v>
       </c>
       <c r="E6" t="n">
-        <v>2.95319480751651</v>
+        <v>2.94855270166984</v>
       </c>
       <c r="F6" t="n">
         <v>-0.290767344618738</v>
@@ -550,104 +613,159 @@
       <c r="G6" t="n">
         <v>17.5934929069274</v>
       </c>
+      <c r="H6" t="n">
+        <v>4.87329783340303</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.0206323168035953</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.00155117383677</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0939299955693398</v>
+        <v>0.0952591936198494</v>
       </c>
       <c r="D7" t="n">
-        <v>0.219618266406986</v>
+        <v>0.222915712288334</v>
       </c>
       <c r="E7" t="n">
-        <v>2.60571749545656</v>
+        <v>2.61438616613004</v>
       </c>
       <c r="F7" t="n">
-        <v>2.37935339879706</v>
+        <v>2.37935339879707</v>
       </c>
       <c r="G7" t="n">
         <v>39.4314407849418</v>
       </c>
+      <c r="H7" t="n">
+        <v>4.85947776877154</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.0131358177041859</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.93641978228733</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>0.310146211785556</v>
+        <v>0.357532379004772</v>
       </c>
       <c r="D8" t="n">
-        <v>0.602427639066635</v>
+        <v>0.649241484408256</v>
       </c>
       <c r="E8" t="n">
-        <v>1.23795205887821</v>
+        <v>1.03402450661125</v>
       </c>
       <c r="F8" t="n">
-        <v>2.76593555491884</v>
+        <v>7.92256352045952</v>
       </c>
       <c r="G8" t="n">
-        <v>78.6849396016568</v>
+        <v>88.3849358851764</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5.06727419573212</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.0550399314911974</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.91962243180292</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>0.334514842711564</v>
+        <v>0.35054533060668</v>
       </c>
       <c r="D9" t="n">
-        <v>0.666307752543019</v>
+        <v>0.644669958902824</v>
       </c>
       <c r="E9" t="n">
-        <v>1.07904672660092</v>
+        <v>1.3736581671586</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.14137908795032</v>
+        <v>14.8658530386248</v>
       </c>
       <c r="G9" t="n">
-        <v>339.336382656525</v>
+        <v>417.524318143391</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.70578594621865</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.0439086026455837</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.9690296331638</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10"/>
-      <c r="D10"/>
-      <c r="E10"/>
-      <c r="F10"/>
-      <c r="G10"/>
+        <v>13</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.297546012269939</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.513182970754097</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.07569892188849</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5.59461875932789</v>
+      </c>
+      <c r="G10" t="n">
+        <v>83.7144528539933</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.65430826080991</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.00776900936684576</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.1054916040229</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
       <c r="C11" t="n">
-        <v>0.163491360212672</v>
+        <v>0.163048294195835</v>
       </c>
       <c r="D11" t="n">
-        <v>0.236785111906135</v>
+        <v>0.225516164711312</v>
       </c>
       <c r="E11" t="n">
-        <v>3.91037315514876</v>
+        <v>2.47671731389969</v>
       </c>
       <c r="F11" t="n">
         <v>-1.87959438539939</v>
@@ -655,307 +773,462 @@
       <c r="G11" t="n">
         <v>13.1827363509551</v>
       </c>
+      <c r="H11" t="n">
+        <v>4.96647598610492</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.0348164715282239</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.85788502446393</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12"/>
-      <c r="G12"/>
+        <v>15</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.19972733469666</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.408838316443099</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.97339897647153</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-1.22054339945386</v>
+      </c>
+      <c r="G12" t="n">
+        <v>21.9157651920464</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.92383757331388</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.000794789805851788</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.96428564315311</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="E13"/>
-      <c r="F13"/>
-      <c r="G13"/>
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.21881390593047</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.443130868451156</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.81938776247825</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5.85906588350682</v>
+      </c>
+      <c r="G13" t="n">
+        <v>117.381599407465</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.21162033401094</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.00435914338317816</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.27901162255057</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0958499483089647</v>
+        <v>0.0967109747784594</v>
       </c>
       <c r="D14" t="n">
-        <v>0.208802205050974</v>
+        <v>0.210988900298457</v>
       </c>
       <c r="E14" t="n">
-        <v>2.80686466616841</v>
+        <v>2.80900383661809</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.937840540341539</v>
+        <v>-0.177545799566456</v>
       </c>
       <c r="G14" t="n">
-        <v>23.9353807582578</v>
+        <v>19.0049644953156</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.75355310387526</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.00861025913291332</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.96320960656554</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0899424014178112</v>
+        <v>0.0889570552147239</v>
       </c>
       <c r="D15" t="n">
-        <v>0.207561420642828</v>
+        <v>0.205987054927493</v>
       </c>
       <c r="E15" t="n">
-        <v>2.45210132213632</v>
+        <v>2.47274498056444</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.418064760371925</v>
+        <v>-0.354055777915894</v>
       </c>
       <c r="G15" t="n">
-        <v>11.4786086562827</v>
+        <v>11.4976218131692</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.71953709953727</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.0164790974393694</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.98014497422371</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0704474966770049</v>
+        <v>0.0663769597818678</v>
       </c>
       <c r="D16" t="n">
-        <v>0.163173855721279</v>
+        <v>0.157324260389907</v>
       </c>
       <c r="E16" t="n">
-        <v>2.80984099881588</v>
+        <v>2.83956877267308</v>
       </c>
       <c r="F16" t="n">
-        <v>0.739050572733899</v>
+        <v>0.799115470757146</v>
       </c>
       <c r="G16" t="n">
-        <v>10.9924612812438</v>
+        <v>12.1098812520154</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.48064398154436</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.0102240226122585</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.07756292005574</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>0.102052872544676</v>
+        <v>0.100800954328562</v>
       </c>
       <c r="D17" t="n">
-        <v>0.225304617973403</v>
+        <v>0.226955446976792</v>
       </c>
       <c r="E17" t="n">
-        <v>2.50881375230642</v>
+        <v>2.54340228720561</v>
       </c>
       <c r="F17" t="n">
-        <v>1.74401935510359</v>
+        <v>1.94329809811089</v>
       </c>
       <c r="G17" t="n">
-        <v>33.9540592100711</v>
+        <v>36.4816694955961</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.83156267113678</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.022501477503838</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.93916897967167</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
         <v>15</v>
       </c>
-      <c r="B18" t="s">
-        <v>12</v>
-      </c>
       <c r="C18" t="n">
-        <v>0.0911239107960419</v>
+        <v>0.0812031356509884</v>
       </c>
       <c r="D18" t="n">
-        <v>0.215774827694079</v>
+        <v>0.206929310097403</v>
       </c>
       <c r="E18" t="n">
-        <v>2.64500822858612</v>
+        <v>2.58028567374465</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.880337114126608</v>
+        <v>0.513949976939581</v>
       </c>
       <c r="G18" t="n">
-        <v>38.621631834272</v>
+        <v>33.6611768019715</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.58310055252752</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.044147663894722</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.06755324255133</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>0.111800324915079</v>
+        <v>0.115627130197682</v>
       </c>
       <c r="D19" t="n">
-        <v>0.260317717474662</v>
+        <v>0.265297045576988</v>
       </c>
       <c r="E19" t="n">
-        <v>2.31734724008197</v>
+        <v>2.21079480682289</v>
       </c>
       <c r="F19" t="n">
-        <v>2.30260556777371</v>
+        <v>2.6077326268063</v>
       </c>
       <c r="G19" t="n">
-        <v>48.2051695773128</v>
+        <v>58.4568682701251</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.71498566498441</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-0.0368777371203532</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.05551140369506</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0451927337173239</v>
+        <v>0.0683367416496251</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0938271338711843</v>
+        <v>0.140100196779332</v>
       </c>
       <c r="E20" t="n">
-        <v>3.30362050153608</v>
+        <v>3.0752696374158</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.290066365485498</v>
+        <v>-0.328419259706014</v>
       </c>
       <c r="G20" t="n">
-        <v>5.61332951565745</v>
+        <v>7.67845834881439</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.68265702948501</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.0227727492911064</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.00987969045604</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0443066016836509</v>
+        <v>0.0530845262440355</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0860304627306064</v>
+        <v>0.124427467503238</v>
       </c>
       <c r="E21" t="n">
-        <v>3.55462703307353</v>
+        <v>3.20535547361398</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.507245546416746</v>
+        <v>-0.133928976045048</v>
       </c>
       <c r="G21" t="n">
-        <v>7.44580310582853</v>
+        <v>6.81539259422158</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.80043561409858</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.00121668957037143</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.93476513630335</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C22" t="n">
-        <v>0.173091123910796</v>
+        <v>0.0366394001363327</v>
       </c>
       <c r="D22" t="n">
-        <v>0.248869546555533</v>
+        <v>0.0869751989990278</v>
       </c>
       <c r="E22" t="n">
-        <v>3.38654768167346</v>
+        <v>3.33806970018669</v>
       </c>
       <c r="F22" t="n">
-        <v>0.494482673458339</v>
+        <v>0.503470111835784</v>
       </c>
       <c r="G22" t="n">
-        <v>12.6269657571194</v>
+        <v>5.61595548815959</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4.60549638694478</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.0575500585117578</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.14801048530793</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0573032048441885</v>
+        <v>0.0550443081117928</v>
       </c>
       <c r="D23" t="n">
-        <v>0.144488812362079</v>
+        <v>0.143070573853828</v>
       </c>
       <c r="E23" t="n">
-        <v>2.84506444423159</v>
+        <v>2.88811186437177</v>
       </c>
       <c r="F23" t="n">
-        <v>0.736277432110608</v>
+        <v>0.813431703983661</v>
       </c>
       <c r="G23" t="n">
-        <v>17.7952620065376</v>
+        <v>16.9074669103684</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4.59687377377341</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.0141893394523423</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.02438477892547</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0575985821887461</v>
+        <v>0.0547886843899114</v>
       </c>
       <c r="D24" t="n">
-        <v>0.13815579128666</v>
+        <v>0.132343862973588</v>
       </c>
       <c r="E24" t="n">
-        <v>2.96328437151777</v>
+        <v>3.0614876964582</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.334887482419656</v>
+        <v>-0.16742842869345</v>
       </c>
       <c r="G24" t="n">
-        <v>13.4862683618155</v>
+        <v>11.8657297756999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.72048706348016</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.0081151799898243</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.03316635959874</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" t="s">
         <v>16</v>
       </c>
-      <c r="B25" t="s">
-        <v>13</v>
-      </c>
       <c r="C25" t="n">
-        <v>0.0666075911977551</v>
+        <v>0.0697852760736196</v>
       </c>
       <c r="D25" t="n">
-        <v>0.180971508720854</v>
+        <v>0.185348476168797</v>
       </c>
       <c r="E25" t="n">
-        <v>2.58537455920498</v>
+        <v>2.72177118753383</v>
       </c>
       <c r="F25" t="n">
-        <v>1.09831542668347</v>
+        <v>1.74840462297998</v>
       </c>
       <c r="G25" t="n">
-        <v>21.1681463446053</v>
+        <v>28.083308269802</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.70936451704988</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.00167840376713394</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.00386582234425</v>
       </c>
     </row>
   </sheetData>
@@ -974,129 +1247,174 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H1" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="I1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0935361591099296</v>
+        <v>0.0916127016587139</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0934869295525033</v>
+        <v>0.0928340149965917</v>
       </c>
       <c r="D2" t="n">
-        <v>0.213489107426204</v>
+        <v>0.212247003044507</v>
       </c>
       <c r="E2" t="n">
-        <v>0.212288516372527</v>
+        <v>0.20895910519793</v>
       </c>
       <c r="F2" t="n">
-        <v>2.58999603468252</v>
+        <v>2.57596672627146</v>
       </c>
       <c r="G2" t="n">
-        <v>0.424905513461854</v>
+        <v>0.888749099188595</v>
       </c>
       <c r="H2" t="n">
-        <v>27.86455188624</v>
+        <v>28.5353636880322</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.68056384560093</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.0168619490355185</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.01385852112717</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B3" t="n">
-        <v>0.269384138236597</v>
+        <v>0.264535542784059</v>
       </c>
       <c r="C3" t="n">
-        <v>0.310146211785556</v>
+        <v>0.258179959100205</v>
       </c>
       <c r="D3" t="n">
-        <v>0.501840167838596</v>
+        <v>0.480763293945124</v>
       </c>
       <c r="E3" t="n">
-        <v>0.602427639066635</v>
+        <v>0.478156919602626</v>
       </c>
       <c r="F3" t="n">
-        <v>2.07579064687596</v>
+        <v>1.79214760808463</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.41834597281029</v>
+        <v>5.19032723617764</v>
       </c>
       <c r="H3" t="n">
-        <v>143.734686203046</v>
+        <v>123.683967972171</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.75488371603174</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0.00179370002112241</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.01588765985954</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0740166395904101</v>
+        <v>0.0562798227675528</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0574508935164673</v>
+        <v>0.0549164962508521</v>
       </c>
       <c r="D4" t="n">
-        <v>0.148723875921153</v>
+        <v>0.135377629379635</v>
       </c>
       <c r="E4" t="n">
-        <v>0.14132230182437</v>
+        <v>0.13622202987646</v>
       </c>
       <c r="F4" t="n">
-        <v>3.10641976520623</v>
+        <v>3.04834425993005</v>
       </c>
       <c r="G4" t="n">
-        <v>0.199479356321753</v>
+        <v>0.405921629059152</v>
       </c>
       <c r="H4" t="n">
-        <v>13.0226291819273</v>
+        <v>12.827718564511</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.6858857308053</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0.0128572902796419</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.02567871215596</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0731551223354502</v>
+        <v>0.0719243833997932</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0733274257864422</v>
+        <v>0.0693398316349136</v>
       </c>
       <c r="D5" t="n">
-        <v>0.159345770792143</v>
+        <v>0.164255348168074</v>
       </c>
       <c r="E5" t="n">
-        <v>0.157978124689735</v>
+        <v>0.163681974256309</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9745989682857</v>
+        <v>2.97589292167746</v>
       </c>
       <c r="G5" t="n">
         <v>0.458159895126449</v>
       </c>
       <c r="H5" t="n">
         <v>15.5205376588335</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.7388687052737</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.00522553838031825</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.95571634884829</v>
       </c>
     </row>
   </sheetData>

--- a/results/consolidated/Distributional_Metrics.xlsx
+++ b/results/consolidated/Distributional_Metrics.xlsx
@@ -470,30 +470,14 @@
       <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.076650420912716</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.160389152361435</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3.15631031146281</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-0.418138070850439</v>
-      </c>
-      <c r="G2" t="n">
-        <v>8.97776447874992</v>
-      </c>
-      <c r="H2" t="n">
-        <v>4.63308831976915</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-0.0138493356016358</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.96197909302964</v>
-      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
@@ -502,30 +486,14 @@
       <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.0654260818195244</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.147674105852211</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3.15524434405118</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-0.12881552296952</v>
-      </c>
-      <c r="G3" t="n">
-        <v>7.18162205654484</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4.61893274833412</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.000438873877783509</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.84982224717142</v>
-      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
@@ -534,30 +502,14 @@
       <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.0555309407768424</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.116236848525405</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3.25856947811445</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.515500113795784</v>
-      </c>
-      <c r="G4" t="n">
-        <v>6.36143305583346</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.74373578764116</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-0.0370981127070806</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.97589345631208</v>
-      </c>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -566,30 +518,14 @@
       <c r="B5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.0711859400383991</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.171341473829878</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2.72229452863646</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.691826796604542</v>
-      </c>
-      <c r="G5" t="n">
-        <v>13.5774726700034</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4.70467977372323</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.0266518432484328</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.0086323404525</v>
-      </c>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
@@ -598,30 +534,14 @@
       <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.0674937232314281</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.166974796151183</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2.94855270166984</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-0.290767344618738</v>
-      </c>
-      <c r="G6" t="n">
-        <v>17.5934929069274</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4.87329783340303</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-0.0206323168035953</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.00155117383677</v>
-      </c>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
@@ -630,30 +550,14 @@
       <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.0952591936198494</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.222915712288334</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2.61438616613004</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2.37935339879707</v>
-      </c>
-      <c r="G7" t="n">
-        <v>39.4314407849418</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4.85947776877154</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.0131358177041859</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.93641978228733</v>
-      </c>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7"/>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -662,30 +566,14 @@
       <c r="B8" t="s">
         <v>11</v>
       </c>
-      <c r="C8" t="n">
-        <v>0.357532379004772</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.649241484408256</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1.03402450661125</v>
-      </c>
-      <c r="F8" t="n">
-        <v>7.92256352045952</v>
-      </c>
-      <c r="G8" t="n">
-        <v>88.3849358851764</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5.06727419573212</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.0550399314911974</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.91962243180292</v>
-      </c>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -694,30 +582,14 @@
       <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.35054533060668</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.644669958902824</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.3736581671586</v>
-      </c>
-      <c r="F9" t="n">
-        <v>14.8658530386248</v>
-      </c>
-      <c r="G9" t="n">
-        <v>417.524318143391</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4.70578594621865</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-0.0439086026455837</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.9690296331638</v>
-      </c>
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -726,30 +598,14 @@
       <c r="B10" t="s">
         <v>13</v>
       </c>
-      <c r="C10" t="n">
-        <v>0.297546012269939</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.513182970754097</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2.07569892188849</v>
-      </c>
-      <c r="F10" t="n">
-        <v>5.59461875932789</v>
-      </c>
-      <c r="G10" t="n">
-        <v>83.7144528539933</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4.65430826080991</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.00776900936684576</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.1054916040229</v>
-      </c>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
@@ -758,30 +614,14 @@
       <c r="B11" t="s">
         <v>14</v>
       </c>
-      <c r="C11" t="n">
-        <v>0.163048294195835</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.225516164711312</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2.47671731389969</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-1.87959438539939</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13.1827363509551</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4.96647598610492</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-0.0348164715282239</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2.85788502446393</v>
-      </c>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -790,30 +630,14 @@
       <c r="B12" t="s">
         <v>15</v>
       </c>
-      <c r="C12" t="n">
-        <v>0.19972733469666</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.408838316443099</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1.97339897647153</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-1.22054339945386</v>
-      </c>
-      <c r="G12" t="n">
-        <v>21.9157651920464</v>
-      </c>
-      <c r="H12" t="n">
-        <v>4.92383757331388</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.000794789805851788</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.96428564315311</v>
-      </c>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
@@ -855,28 +679,28 @@
         <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0967109747784594</v>
+        <v>0.103612815269257</v>
       </c>
       <c r="D14" t="n">
-        <v>0.210988900298457</v>
+        <v>0.216898782998281</v>
       </c>
       <c r="E14" t="n">
-        <v>2.80900383661809</v>
+        <v>2.8171178981461</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.177545799566456</v>
+        <v>-0.0844613515334189</v>
       </c>
       <c r="G14" t="n">
-        <v>19.0049644953156</v>
+        <v>22.1600723958877</v>
       </c>
       <c r="H14" t="n">
-        <v>4.75355310387526</v>
+        <v>4.90704670049743</v>
       </c>
       <c r="I14" t="n">
-        <v>0.00861025913291332</v>
+        <v>0.0453003573810095</v>
       </c>
       <c r="J14" t="n">
-        <v>2.96320960656554</v>
+        <v>2.95654875967296</v>
       </c>
     </row>
     <row r="15">
@@ -887,28 +711,28 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0889570552147239</v>
+        <v>0.0940695296523517</v>
       </c>
       <c r="D15" t="n">
-        <v>0.205987054927493</v>
+        <v>0.202861718601771</v>
       </c>
       <c r="E15" t="n">
-        <v>2.47274498056444</v>
+        <v>2.37928056229627</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.354055777915894</v>
+        <v>-0.407551906535834</v>
       </c>
       <c r="G15" t="n">
-        <v>11.4976218131692</v>
+        <v>10.300691851273</v>
       </c>
       <c r="H15" t="n">
-        <v>4.71953709953727</v>
+        <v>4.95802884946734</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0164790974393694</v>
+        <v>0.0290231689780977</v>
       </c>
       <c r="J15" t="n">
-        <v>2.98014497422371</v>
+        <v>3.00592470782407</v>
       </c>
     </row>
     <row r="16">
@@ -919,28 +743,28 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0663769597818678</v>
+        <v>0.0674846625766871</v>
       </c>
       <c r="D16" t="n">
-        <v>0.157324260389907</v>
+        <v>0.153251191339016</v>
       </c>
       <c r="E16" t="n">
-        <v>2.83956877267308</v>
+        <v>2.75629942312616</v>
       </c>
       <c r="F16" t="n">
-        <v>0.799115470757146</v>
+        <v>0.681813007300252</v>
       </c>
       <c r="G16" t="n">
-        <v>12.1098812520154</v>
+        <v>10.1849121067362</v>
       </c>
       <c r="H16" t="n">
-        <v>4.48064398154436</v>
+        <v>4.18775387370334</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0102240226122585</v>
+        <v>-0.0204855625536789</v>
       </c>
       <c r="J16" t="n">
-        <v>3.07756292005574</v>
+        <v>3.01360337600613</v>
       </c>
     </row>
     <row r="17">
@@ -951,28 +775,28 @@
         <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>0.100800954328562</v>
+        <v>0.116223585548739</v>
       </c>
       <c r="D17" t="n">
-        <v>0.226955446976792</v>
+        <v>0.242296893614514</v>
       </c>
       <c r="E17" t="n">
-        <v>2.54340228720561</v>
+        <v>2.45518544857968</v>
       </c>
       <c r="F17" t="n">
-        <v>1.94329809811089</v>
+        <v>1.94668115176739</v>
       </c>
       <c r="G17" t="n">
-        <v>36.4816694955961</v>
+        <v>32.0688816727918</v>
       </c>
       <c r="H17" t="n">
-        <v>4.83156267113678</v>
+        <v>5.45596316061667</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.022501477503838</v>
+        <v>-0.0130074696341871</v>
       </c>
       <c r="J17" t="n">
-        <v>2.93916897967167</v>
+        <v>2.7876083116728</v>
       </c>
     </row>
     <row r="18">
@@ -983,28 +807,28 @@
         <v>15</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0812031356509884</v>
+        <v>0.0906612133605999</v>
       </c>
       <c r="D18" t="n">
-        <v>0.206929310097403</v>
+        <v>0.224962994149443</v>
       </c>
       <c r="E18" t="n">
-        <v>2.58028567374465</v>
+        <v>2.53213305164275</v>
       </c>
       <c r="F18" t="n">
-        <v>0.513949976939581</v>
+        <v>-1.12494919312209</v>
       </c>
       <c r="G18" t="n">
-        <v>33.6611768019715</v>
+        <v>44.7416265363179</v>
       </c>
       <c r="H18" t="n">
-        <v>4.58310055252752</v>
+        <v>4.44175004052208</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.044147663894722</v>
+        <v>0.0132024529486022</v>
       </c>
       <c r="J18" t="n">
-        <v>3.06755324255133</v>
+        <v>3.15492997191924</v>
       </c>
     </row>
     <row r="19">
@@ -1015,28 +839,28 @@
         <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>0.115627130197682</v>
+        <v>0.139740967961827</v>
       </c>
       <c r="D19" t="n">
-        <v>0.265297045576988</v>
+        <v>0.316870835444162</v>
       </c>
       <c r="E19" t="n">
-        <v>2.21079480682289</v>
+        <v>2.12627831873709</v>
       </c>
       <c r="F19" t="n">
-        <v>2.6077326268063</v>
+        <v>4.65444605205222</v>
       </c>
       <c r="G19" t="n">
-        <v>58.4568682701251</v>
+        <v>96.4068715371316</v>
       </c>
       <c r="H19" t="n">
-        <v>4.71498566498441</v>
+        <v>4.70380573051862</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0368777371203532</v>
+        <v>-0.0425277603258377</v>
       </c>
       <c r="J19" t="n">
-        <v>3.05551140369506</v>
+        <v>2.96239964588089</v>
       </c>
     </row>
     <row r="20">
@@ -1047,28 +871,28 @@
         <v>11</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0683367416496251</v>
+        <v>0.0780504430811179</v>
       </c>
       <c r="D20" t="n">
-        <v>0.140100196779332</v>
+        <v>0.150566063719283</v>
       </c>
       <c r="E20" t="n">
-        <v>3.0752696374158</v>
+        <v>3.12242391993693</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.328419259706014</v>
+        <v>-0.354841740580612</v>
       </c>
       <c r="G20" t="n">
-        <v>7.67845834881439</v>
+        <v>7.42227540527588</v>
       </c>
       <c r="H20" t="n">
-        <v>4.68265702948501</v>
+        <v>5.06727603117541</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0227727492911064</v>
+        <v>0.0550399406070241</v>
       </c>
       <c r="J20" t="n">
-        <v>3.00987969045604</v>
+        <v>2.91962262442509</v>
       </c>
     </row>
     <row r="21">
@@ -1079,28 +903,28 @@
         <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0530845262440355</v>
+        <v>0.0497614178595774</v>
       </c>
       <c r="D21" t="n">
-        <v>0.124427467503238</v>
+        <v>0.101648462987334</v>
       </c>
       <c r="E21" t="n">
-        <v>3.20535547361398</v>
+        <v>3.51025653099684</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.133928976045048</v>
+        <v>-0.487933199855872</v>
       </c>
       <c r="G21" t="n">
-        <v>6.81539259422158</v>
+        <v>7.86831910742023</v>
       </c>
       <c r="H21" t="n">
-        <v>4.80043561409858</v>
+        <v>4.91286432552617</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.00121668957037143</v>
+        <v>-0.00923984709617871</v>
       </c>
       <c r="J21" t="n">
-        <v>2.93476513630335</v>
+        <v>2.89406436499302</v>
       </c>
     </row>
     <row r="22">
@@ -1111,28 +935,28 @@
         <v>13</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0366394001363327</v>
+        <v>0.0494205862304022</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0869751989990278</v>
+        <v>0.105539548962002</v>
       </c>
       <c r="E22" t="n">
-        <v>3.33806970018669</v>
+        <v>3.42502086233003</v>
       </c>
       <c r="F22" t="n">
-        <v>0.503470111835784</v>
+        <v>0.554211243543568</v>
       </c>
       <c r="G22" t="n">
-        <v>5.61595548815959</v>
+        <v>5.58850630811692</v>
       </c>
       <c r="H22" t="n">
-        <v>4.60549638694478</v>
+        <v>4.97077248924655</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0575500585117578</v>
+        <v>-0.0147654006844162</v>
       </c>
       <c r="J22" t="n">
-        <v>3.14801048530793</v>
+        <v>3.03203445463235</v>
       </c>
     </row>
     <row r="23">
@@ -1143,28 +967,28 @@
         <v>14</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0550443081117928</v>
+        <v>0.0589638718473074</v>
       </c>
       <c r="D23" t="n">
-        <v>0.143070573853828</v>
+        <v>0.159000935020131</v>
       </c>
       <c r="E23" t="n">
-        <v>2.88811186437177</v>
+        <v>2.83806191331147</v>
       </c>
       <c r="F23" t="n">
-        <v>0.813431703983661</v>
+        <v>0.89818315334654</v>
       </c>
       <c r="G23" t="n">
-        <v>16.9074669103684</v>
+        <v>19.6669577671629</v>
       </c>
       <c r="H23" t="n">
-        <v>4.59687377377341</v>
+        <v>4.85782027308368</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0141893394523423</v>
+        <v>-0.0368970841472968</v>
       </c>
       <c r="J23" t="n">
-        <v>3.02438477892547</v>
+        <v>2.89479634085416</v>
       </c>
     </row>
     <row r="24">
@@ -1175,28 +999,28 @@
         <v>15</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0547886843899114</v>
+        <v>0.0579413769597819</v>
       </c>
       <c r="D24" t="n">
-        <v>0.132343862973588</v>
+        <v>0.145065333346745</v>
       </c>
       <c r="E24" t="n">
-        <v>3.0614876964582</v>
+        <v>2.92926223607011</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.16742842869345</v>
+        <v>-0.410755045639093</v>
       </c>
       <c r="G24" t="n">
-        <v>11.8657297756999</v>
+        <v>15.4639777693719</v>
       </c>
       <c r="H24" t="n">
-        <v>4.72048706348016</v>
+        <v>4.6735409333808</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0081151799898243</v>
+        <v>-0.0394675527029971</v>
       </c>
       <c r="J24" t="n">
-        <v>3.03316635959874</v>
+        <v>3.08567878470139</v>
       </c>
     </row>
     <row r="25">
@@ -1207,28 +1031,28 @@
         <v>16</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0697852760736196</v>
+        <v>0.0838445807770961</v>
       </c>
       <c r="D25" t="n">
-        <v>0.185348476168797</v>
+        <v>0.209019173367189</v>
       </c>
       <c r="E25" t="n">
-        <v>2.72177118753383</v>
+        <v>2.66463900931426</v>
       </c>
       <c r="F25" t="n">
-        <v>1.74840462297998</v>
+        <v>2.62307094894505</v>
       </c>
       <c r="G25" t="n">
-        <v>28.083308269802</v>
+        <v>40.2504676664292</v>
       </c>
       <c r="H25" t="n">
-        <v>4.70936451704988</v>
+        <v>4.40196978163542</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.00167840376713394</v>
+        <v>0.0849089627391667</v>
       </c>
       <c r="J25" t="n">
-        <v>3.00386582234425</v>
+        <v>3.09616547350844</v>
       </c>
     </row>
   </sheetData>
@@ -1282,34 +1106,34 @@
         <v>18</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0916127016587139</v>
+        <v>0.10196546239491</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0928340149965917</v>
+        <v>0.0988411724608044</v>
       </c>
       <c r="D2" t="n">
-        <v>0.212247003044507</v>
+        <v>0.226190402691198</v>
       </c>
       <c r="E2" t="n">
-        <v>0.20895910519793</v>
+        <v>0.220930888573862</v>
       </c>
       <c r="F2" t="n">
-        <v>2.57596672627146</v>
+        <v>2.51104911708801</v>
       </c>
       <c r="G2" t="n">
-        <v>0.888749099188595</v>
+        <v>0.944329626654751</v>
       </c>
       <c r="H2" t="n">
-        <v>28.5353636880322</v>
+        <v>35.9771760166897</v>
       </c>
       <c r="I2" t="n">
-        <v>4.68056384560093</v>
+        <v>4.77572472588758</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.0168619490355185</v>
+        <v>0.00191753113233428</v>
       </c>
       <c r="K2" t="n">
-        <v>3.01385852112717</v>
+        <v>2.98016912882935</v>
       </c>
     </row>
     <row r="3">
@@ -1317,34 +1141,34 @@
         <v>17</v>
       </c>
       <c r="B3" t="n">
-        <v>0.264535542784059</v>
+        <v>0.21881390593047</v>
       </c>
       <c r="C3" t="n">
-        <v>0.258179959100205</v>
+        <v>0.21881390593047</v>
       </c>
       <c r="D3" t="n">
-        <v>0.480763293945124</v>
+        <v>0.443130868451156</v>
       </c>
       <c r="E3" t="n">
-        <v>0.478156919602626</v>
+        <v>0.443130868451156</v>
       </c>
       <c r="F3" t="n">
-        <v>1.79214760808463</v>
+        <v>1.81938776247825</v>
       </c>
       <c r="G3" t="n">
-        <v>5.19032723617764</v>
+        <v>5.85906588350682</v>
       </c>
       <c r="H3" t="n">
-        <v>123.683967972171</v>
+        <v>117.381599407465</v>
       </c>
       <c r="I3" t="n">
-        <v>4.75488371603174</v>
+        <v>4.21162033401094</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.00179370002112241</v>
+        <v>0.00435914338317816</v>
       </c>
       <c r="K3" t="n">
-        <v>3.01588765985954</v>
+        <v>3.27901162255057</v>
       </c>
     </row>
     <row r="4">
@@ -1352,69 +1176,65 @@
         <v>19</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0562798227675528</v>
+        <v>0.0629970461258805</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0549164962508521</v>
+        <v>0.0584526244035447</v>
       </c>
       <c r="D4" t="n">
-        <v>0.135377629379635</v>
+        <v>0.145139919567114</v>
       </c>
       <c r="E4" t="n">
-        <v>0.13622202987646</v>
+        <v>0.147815698533014</v>
       </c>
       <c r="F4" t="n">
-        <v>3.04834425993005</v>
+        <v>3.08161074532661</v>
       </c>
       <c r="G4" t="n">
-        <v>0.405921629059152</v>
+        <v>0.47032255995993</v>
       </c>
       <c r="H4" t="n">
-        <v>12.827718564511</v>
+        <v>16.0434173372962</v>
       </c>
       <c r="I4" t="n">
-        <v>4.6858857308053</v>
+        <v>4.814040639008</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0128572902796419</v>
+        <v>0.006596503119217</v>
       </c>
       <c r="K4" t="n">
-        <v>3.02567871215596</v>
+        <v>2.98706034051908</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="n">
-        <v>0.0719243833997932</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.0693398316349136</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.164255348168074</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.163681974256309</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2.97589292167746</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.458159895126449</v>
-      </c>
-      <c r="H5" t="n">
-        <v>15.5205376588335</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4.7388687052737</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-0.00522553838031825</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2.95571634884829</v>
+      <c r="B5" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="C5"/>
+      <c r="D5" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="G5" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H5" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="I5" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="J5" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="K5" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
   </sheetData>

--- a/results/consolidated/Distributional_Metrics.xlsx
+++ b/results/consolidated/Distributional_Metrics.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">Model</t>
   </si>
@@ -54,13 +54,34 @@
     <t xml:space="preserve">GBPUSD</t>
   </si>
   <si>
+    <t xml:space="preserve">GBPCNY</t>
+  </si>
+  <si>
     <t xml:space="preserve">USDZAR</t>
   </si>
   <si>
+    <t xml:space="preserve">GBPZAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EURZAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X</t>
+  </si>
+  <si>
     <t xml:space="preserve">NVDA</t>
   </si>
   <si>
     <t xml:space="preserve">MSFT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WMT</t>
   </si>
   <si>
     <t xml:space="preserve">AMZN</t>
@@ -561,10 +582,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
         <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
       </c>
       <c r="C8"/>
       <c r="D8"/>
@@ -577,10 +598,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C9"/>
       <c r="D9"/>
@@ -593,10 +614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C10"/>
       <c r="D10"/>
@@ -609,10 +630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C11"/>
       <c r="D11"/>
@@ -625,10 +646,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C12"/>
       <c r="D12"/>
@@ -641,419 +662,659 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.21881390593047</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.443130868451156</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.81938776247825</v>
-      </c>
-      <c r="F13" t="n">
-        <v>5.85906588350682</v>
-      </c>
-      <c r="G13" t="n">
-        <v>117.381599407465</v>
-      </c>
-      <c r="H13" t="n">
-        <v>4.21162033401094</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.00435914338317816</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.27901162255057</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.103612815269257</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.216898782998281</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2.8171178981461</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-0.0844613515334189</v>
-      </c>
-      <c r="G14" t="n">
-        <v>22.1600723958877</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4.90704670049743</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.0453003573810095</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.95654875967296</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.0940695296523517</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.202861718601771</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2.37928056229627</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-0.407551906535834</v>
-      </c>
-      <c r="G15" t="n">
-        <v>10.300691851273</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4.95802884946734</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.0290231689780977</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.00592470782407</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.0674846625766871</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.153251191339016</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2.75629942312616</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.681813007300252</v>
-      </c>
-      <c r="G16" t="n">
-        <v>10.1849121067362</v>
-      </c>
-      <c r="H16" t="n">
-        <v>4.18775387370334</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-0.0204855625536789</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.01360337600613</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.116223585548739</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.242296893614514</v>
-      </c>
-      <c r="E17" t="n">
-        <v>2.45518544857968</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1.94668115176739</v>
-      </c>
-      <c r="G17" t="n">
-        <v>32.0688816727918</v>
-      </c>
-      <c r="H17" t="n">
-        <v>5.45596316061667</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-0.0130074696341871</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.7876083116728</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.0906612133605999</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.224962994149443</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2.53213305164275</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-1.12494919312209</v>
-      </c>
-      <c r="G18" t="n">
-        <v>44.7416265363179</v>
-      </c>
-      <c r="H18" t="n">
-        <v>4.44175004052208</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.0132024529486022</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.15492997191924</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.139740967961827</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.316870835444162</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2.12627831873709</v>
-      </c>
-      <c r="F19" t="n">
-        <v>4.65444605205222</v>
-      </c>
-      <c r="G19" t="n">
-        <v>96.4068715371316</v>
-      </c>
-      <c r="H19" t="n">
-        <v>4.70380573051862</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-0.0425277603258377</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.96239964588089</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.0780504430811179</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.150566063719283</v>
-      </c>
-      <c r="E20" t="n">
-        <v>3.12242391993693</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-0.354841740580612</v>
-      </c>
-      <c r="G20" t="n">
-        <v>7.42227540527588</v>
-      </c>
-      <c r="H20" t="n">
-        <v>5.06727603117541</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.0550399406070241</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.91962262442509</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="I20"/>
+      <c r="J20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.0497614178595774</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.101648462987334</v>
-      </c>
-      <c r="E21" t="n">
-        <v>3.51025653099684</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-0.487933199855872</v>
-      </c>
-      <c r="G21" t="n">
-        <v>7.86831910742023</v>
-      </c>
-      <c r="H21" t="n">
-        <v>4.91286432552617</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-0.00923984709617871</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.89406436499302</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21"/>
+      <c r="I21"/>
+      <c r="J21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.0494205862304022</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.105539548962002</v>
-      </c>
-      <c r="E22" t="n">
-        <v>3.42502086233003</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.554211243543568</v>
-      </c>
-      <c r="G22" t="n">
-        <v>5.58850630811692</v>
-      </c>
-      <c r="H22" t="n">
-        <v>4.97077248924655</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-0.0147654006844162</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.03203445463235</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="I22"/>
+      <c r="J22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
         <v>19</v>
       </c>
-      <c r="B23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.0589638718473074</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.159000935020131</v>
-      </c>
-      <c r="E23" t="n">
-        <v>2.83806191331147</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.89818315334654</v>
-      </c>
-      <c r="G23" t="n">
-        <v>19.6669577671629</v>
-      </c>
-      <c r="H23" t="n">
-        <v>4.85782027308368</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-0.0368970841472968</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2.89479634085416</v>
-      </c>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.0579413769597819</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.145065333346745</v>
-      </c>
-      <c r="E24" t="n">
-        <v>2.92926223607011</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-0.410755045639093</v>
-      </c>
-      <c r="G24" t="n">
-        <v>15.4639777693719</v>
-      </c>
-      <c r="H24" t="n">
-        <v>4.6735409333808</v>
-      </c>
-      <c r="I24" t="n">
-        <v>-0.0394675527029971</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3.08567878470139</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24"/>
+      <c r="I24"/>
+      <c r="J24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25"/>
+      <c r="D25"/>
+      <c r="E25"/>
+      <c r="F25"/>
+      <c r="G25"/>
+      <c r="H25"/>
+      <c r="I25"/>
+      <c r="J25"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26"/>
+      <c r="D26"/>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26"/>
+      <c r="I26"/>
+      <c r="J26"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27"/>
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27"/>
+      <c r="H27"/>
+      <c r="I27"/>
+      <c r="J27"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28"/>
+      <c r="D28"/>
+      <c r="E28"/>
+      <c r="F28"/>
+      <c r="G28"/>
+      <c r="H28"/>
+      <c r="I28"/>
+      <c r="J28"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29"/>
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29"/>
+      <c r="I29"/>
+      <c r="J29"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
+      <c r="I30"/>
+      <c r="J30"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31"/>
+      <c r="I31"/>
+      <c r="J31"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32"/>
+      <c r="D32"/>
+      <c r="E32"/>
+      <c r="F32"/>
+      <c r="G32"/>
+      <c r="H32"/>
+      <c r="I32"/>
+      <c r="J32"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33"/>
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33"/>
+      <c r="H33"/>
+      <c r="I33"/>
+      <c r="J33"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34"/>
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34"/>
+      <c r="G34"/>
+      <c r="H34"/>
+      <c r="I34"/>
+      <c r="J34"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35"/>
+      <c r="D35"/>
+      <c r="E35"/>
+      <c r="F35"/>
+      <c r="G35"/>
+      <c r="H35"/>
+      <c r="I35"/>
+      <c r="J35"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" t="s">
         <v>19</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C36"/>
+      <c r="D36"/>
+      <c r="E36"/>
+      <c r="F36"/>
+      <c r="G36"/>
+      <c r="H36"/>
+      <c r="I36"/>
+      <c r="J36"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37"/>
+      <c r="D37"/>
+      <c r="E37"/>
+      <c r="F37"/>
+      <c r="G37"/>
+      <c r="H37"/>
+      <c r="I37"/>
+      <c r="J37"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38"/>
+      <c r="D38"/>
+      <c r="E38"/>
+      <c r="F38"/>
+      <c r="G38"/>
+      <c r="H38"/>
+      <c r="I38"/>
+      <c r="J38"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39"/>
+      <c r="D39"/>
+      <c r="E39"/>
+      <c r="F39"/>
+      <c r="G39"/>
+      <c r="H39"/>
+      <c r="I39"/>
+      <c r="J39"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40"/>
+      <c r="D40"/>
+      <c r="E40"/>
+      <c r="F40"/>
+      <c r="G40"/>
+      <c r="H40"/>
+      <c r="I40"/>
+      <c r="J40"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>26</v>
+      </c>
+      <c r="B41" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41"/>
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="G41"/>
+      <c r="H41"/>
+      <c r="I41"/>
+      <c r="J41"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>26</v>
+      </c>
+      <c r="B42" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
+      <c r="J42"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>26</v>
+      </c>
+      <c r="B43" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43"/>
+      <c r="D43"/>
+      <c r="E43"/>
+      <c r="F43"/>
+      <c r="G43"/>
+      <c r="H43"/>
+      <c r="I43"/>
+      <c r="J43"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>26</v>
+      </c>
+      <c r="B44" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44"/>
+      <c r="D44"/>
+      <c r="E44"/>
+      <c r="F44"/>
+      <c r="G44"/>
+      <c r="H44"/>
+      <c r="I44"/>
+      <c r="J44"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>26</v>
+      </c>
+      <c r="B45" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45"/>
+      <c r="D45"/>
+      <c r="E45"/>
+      <c r="F45"/>
+      <c r="G45"/>
+      <c r="H45"/>
+      <c r="I45"/>
+      <c r="J45"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>26</v>
+      </c>
+      <c r="B46" t="s">
         <v>16</v>
       </c>
-      <c r="C25" t="n">
-        <v>0.0838445807770961</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.209019173367189</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2.66463900931426</v>
-      </c>
-      <c r="F25" t="n">
-        <v>2.62307094894505</v>
-      </c>
-      <c r="G25" t="n">
-        <v>40.2504676664292</v>
-      </c>
-      <c r="H25" t="n">
-        <v>4.40196978163542</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.0849089627391667</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3.09616547350844</v>
-      </c>
+      <c r="C46"/>
+      <c r="D46"/>
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46"/>
+      <c r="I46"/>
+      <c r="J46"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>26</v>
+      </c>
+      <c r="B47" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47"/>
+      <c r="D47"/>
+      <c r="E47"/>
+      <c r="F47"/>
+      <c r="G47"/>
+      <c r="H47"/>
+      <c r="I47"/>
+      <c r="J47"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>26</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48"/>
+      <c r="D48"/>
+      <c r="E48"/>
+      <c r="F48"/>
+      <c r="G48"/>
+      <c r="H48"/>
+      <c r="I48"/>
+      <c r="J48"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>26</v>
+      </c>
+      <c r="B49" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49"/>
+      <c r="D49"/>
+      <c r="E49"/>
+      <c r="F49"/>
+      <c r="G49"/>
+      <c r="H49"/>
+      <c r="I49"/>
+      <c r="J49"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>26</v>
+      </c>
+      <c r="B50" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50"/>
+      <c r="D50"/>
+      <c r="E50"/>
+      <c r="F50"/>
+      <c r="G50"/>
+      <c r="H50"/>
+      <c r="I50"/>
+      <c r="J50"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>26</v>
+      </c>
+      <c r="B51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51"/>
+      <c r="D51"/>
+      <c r="E51"/>
+      <c r="F51"/>
+      <c r="G51"/>
+      <c r="H51"/>
+      <c r="I51"/>
+      <c r="J51"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>26</v>
+      </c>
+      <c r="B52" t="s">
+        <v>22</v>
+      </c>
+      <c r="C52"/>
+      <c r="D52"/>
+      <c r="E52"/>
+      <c r="F52"/>
+      <c r="G52"/>
+      <c r="H52"/>
+      <c r="I52"/>
+      <c r="J52"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>26</v>
+      </c>
+      <c r="B53" t="s">
+        <v>23</v>
+      </c>
+      <c r="C53"/>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53"/>
+      <c r="G53"/>
+      <c r="H53"/>
+      <c r="I53"/>
+      <c r="J53"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1071,139 +1332,127 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="I1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="J1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0.10196546239491</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.0988411724608044</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.226190402691198</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.220930888573862</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2.51104911708801</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.944329626654751</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.9771760166897</v>
-      </c>
-      <c r="I2" t="n">
-        <v>4.77572472588758</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.00191753113233428</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2.98016912882935</v>
+        <v>25</v>
+      </c>
+      <c r="B2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="E2"/>
+      <c r="F2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="G2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="I2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="J2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="K2" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0.21881390593047</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.21881390593047</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.443130868451156</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.443130868451156</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.81938776247825</v>
-      </c>
-      <c r="G3" t="n">
-        <v>5.85906588350682</v>
-      </c>
-      <c r="H3" t="n">
-        <v>117.381599407465</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4.21162033401094</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.00435914338317816</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.27901162255057</v>
+        <v>24</v>
+      </c>
+      <c r="B3" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="E3"/>
+      <c r="F3" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="G3" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H3" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="I3" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="J3" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="K3" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.0629970461258805</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.0584526244035447</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.145139919567114</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.147815698533014</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3.08161074532661</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.47032255995993</v>
-      </c>
-      <c r="H4" t="n">
-        <v>16.0434173372962</v>
-      </c>
-      <c r="I4" t="n">
-        <v>4.814040639008</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.006596503119217</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2.98706034051908</v>
+        <v>26</v>
+      </c>
+      <c r="B4" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="E4"/>
+      <c r="F4" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="G4" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H4" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="I4" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="J4" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="K4" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="5">
